--- a/AO.xlsx
+++ b/AO.xlsx
@@ -917,6 +917,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1007,7 +1008,7 @@
         <v>8700</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="I3">
         <v>0</v>

--- a/AO.xlsx
+++ b/AO.xlsx
@@ -1252,13 +1252,13 @@
         <v>912861288</v>
       </c>
       <c r="E11">
-        <v>67773.399999999994</v>
+        <v>61273.4</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>67773.399999999994</v>
+        <v>61273.4</v>
       </c>
       <c r="H11">
         <v>0</v>

--- a/AO.xlsx
+++ b/AO.xlsx
@@ -967,13 +967,13 @@
         <v>11</v>
       </c>
       <c r="E2">
-        <v>6700</v>
+        <v>6900</v>
       </c>
       <c r="F2">
         <v>2000</v>
       </c>
       <c r="G2">
-        <v>8700</v>
+        <v>8900</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -999,13 +999,13 @@
         <v>928276274</v>
       </c>
       <c r="E3">
-        <v>6700</v>
+        <v>6900</v>
       </c>
       <c r="F3">
         <v>2000</v>
       </c>
       <c r="G3">
-        <v>8700</v>
+        <v>8900</v>
       </c>
       <c r="H3">
         <v>7500</v>
@@ -1031,16 +1031,16 @@
         <v>930308503</v>
       </c>
       <c r="E4">
-        <v>6700</v>
+        <v>6900</v>
       </c>
       <c r="F4">
         <v>2000</v>
       </c>
       <c r="G4">
-        <v>8700</v>
+        <v>8900</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10000</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1095,13 +1095,13 @@
         <v>977677737</v>
       </c>
       <c r="E6">
-        <v>6700</v>
+        <v>6900</v>
       </c>
       <c r="F6">
         <v>2000</v>
       </c>
       <c r="G6">
-        <v>8700</v>
+        <v>8900</v>
       </c>
       <c r="H6">
         <v>10000</v>
@@ -1127,13 +1127,13 @@
         <v>912672957</v>
       </c>
       <c r="E7">
-        <v>6700</v>
+        <v>6900</v>
       </c>
       <c r="F7">
         <v>2000</v>
       </c>
       <c r="G7">
-        <v>8700</v>
+        <v>8900</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1159,13 +1159,13 @@
         <v>913354650</v>
       </c>
       <c r="E8">
-        <v>6700</v>
+        <v>6900</v>
       </c>
       <c r="F8">
         <v>2000</v>
       </c>
       <c r="G8">
-        <v>8700</v>
+        <v>8900</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1191,19 +1191,19 @@
         <v>920116666</v>
       </c>
       <c r="E9">
-        <v>6700</v>
+        <v>6900</v>
       </c>
       <c r="F9">
         <v>2000</v>
       </c>
       <c r="G9">
-        <v>8700</v>
+        <v>8900</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>3750</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -1220,13 +1220,13 @@
         <v>912609998</v>
       </c>
       <c r="E10">
-        <v>6700</v>
+        <v>6900</v>
       </c>
       <c r="F10">
         <v>2000</v>
       </c>
       <c r="G10">
-        <v>8700</v>
+        <v>8900</v>
       </c>
       <c r="H10">
         <v>10000</v>
@@ -1252,13 +1252,13 @@
         <v>912861288</v>
       </c>
       <c r="E11">
-        <v>61273.4</v>
+        <v>63984.68</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>61273.4</v>
+        <v>63984.68</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1284,13 +1284,13 @@
         <v>912695064</v>
       </c>
       <c r="E12">
-        <v>6700</v>
+        <v>6900</v>
       </c>
       <c r="F12">
         <v>2000</v>
       </c>
       <c r="G12">
-        <v>8700</v>
+        <v>8900</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1313,13 +1313,13 @@
         <v>922956646</v>
       </c>
       <c r="E13">
-        <v>6700</v>
+        <v>6900</v>
       </c>
       <c r="F13">
         <v>2000</v>
       </c>
       <c r="G13">
-        <v>8700</v>
+        <v>8900</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1342,13 +1342,13 @@
         <v>919408998</v>
       </c>
       <c r="E14">
-        <v>6700</v>
+        <v>6900</v>
       </c>
       <c r="F14">
         <v>2000</v>
       </c>
       <c r="G14">
-        <v>8700</v>
+        <v>8900</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1374,13 +1374,13 @@
         <v>912861288</v>
       </c>
       <c r="E15">
-        <v>6700</v>
+        <v>6900</v>
       </c>
       <c r="F15">
         <v>2000</v>
       </c>
       <c r="G15">
-        <v>8700</v>
+        <v>8900</v>
       </c>
       <c r="H15">
         <v>10000</v>
@@ -1445,9 +1445,6 @@
       </c>
       <c r="G17">
         <v>1300</v>
-      </c>
-      <c r="H17">
-        <v>10000</v>
       </c>
       <c r="I17">
         <v>0</v>

--- a/AO.xlsx
+++ b/AO.xlsx
@@ -1199,6 +1199,9 @@
       <c r="G9">
         <v>8900</v>
       </c>
+      <c r="H9">
+        <v>10000</v>
+      </c>
       <c r="I9">
         <v>0</v>
       </c>
@@ -1252,13 +1255,13 @@
         <v>912861288</v>
       </c>
       <c r="E11">
-        <v>63984.68</v>
+        <v>53984.68</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>63984.68</v>
+        <v>53984.68</v>
       </c>
       <c r="H11">
         <v>0</v>
